--- a/FinalReport/Evidence/wav2vec_vs_mfcc/irish_model_summary_charts.xlsx
+++ b/FinalReport/Evidence/wav2vec_vs_mfcc/irish_model_summary_charts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cianan/Documents/College/GitHub/FYP/Experiments/AutoModels/results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cianan/Documents/College/GitHub/FYP/FinalReport/Evidence/wav2vec_vs_mfcc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33809487-A0D8-B04D-BA23-BE4EB0BE3B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D20F56B-E86A-574E-9194-3102573DC3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="1360" windowWidth="38400" windowHeight="21800" firstSheet="4" activeTab="10" xr2:uid="{4FF49A69-2F49-B14A-A75D-0C6888D117A2}"/>
+    <workbookView xWindow="38400" yWindow="1360" windowWidth="38400" windowHeight="21800" firstSheet="4" activeTab="8" xr2:uid="{4FF49A69-2F49-B14A-A75D-0C6888D117A2}"/>
   </bookViews>
   <sheets>
     <sheet name="irish_model_summary_rebuilt" sheetId="1" r:id="rId1"/>
@@ -4721,6 +4721,545 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Irish Dataset:  </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IE" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Average Improvement Over Random Baseline by Model</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Chart4 - relativeAccuracyModel'!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>avg_relative_improvement</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Chart4 - relativeAccuracyModel'!$G$2:$G$12</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>k-NN (k=1)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>k-NN (k=3)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>k-NN (k=5)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>k-NN (k=7)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>k-NN (k=11)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>SVM (RBF Kernel)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Random Forest</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Naive Bayes</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Logistic Regression</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>SVM (Linear)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Logistic Regression (Weighted)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Chart4 - relativeAccuracyModel'!$H$2:$H$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.22058773318991201</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.24318918448075769</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.24736137814645034</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.26890001186548718</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.27021457756549483</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.29743821886594501</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.31737390451873354</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.33499851349043003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.36592986953842538</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.37003461658216513</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.40344671029958601</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C22D-0C45-8A27-A1330C89E94E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="84"/>
+        <c:overlap val="-27"/>
+        <c:axId val="435735456"/>
+        <c:axId val="435670448"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="435735456"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1200"/>
+                  <a:t>Model</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="435670448"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="435670448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IE" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>Relative Improvement </a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB" sz="1200"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-GB"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="435735456"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -7576,6 +8115,473 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Irish</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:t> Dataset: </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Best Model Per Task</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Chart 2 - BestModelPerTask'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>balanced_accuracy_mean</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0070C0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Chart 2 - BestModelPerTask'!$F$2:$F$7</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Dáil Speakers
+Logistic Regression</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Four Provinces
+SVM (Linear)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Ulster, Leinster, and Rest
+SVM (RBF Kernel)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Leinster vs Rest
+Logistic Regression (Weighted)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Ulster vs Rest
+Logistic Regression (Weighted)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Dáil vs Northern Ireland
+Naive Bayes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Chart 2 - BestModelPerTask'!$G$2:$G$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.27210886725816702</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.39387690904640299</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.52408969936051997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.61580000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.74775796701111596</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.78742267907035202</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FC17-C142-8CB0-BC342651D6BF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="50"/>
+        <c:axId val="1389255183"/>
+        <c:axId val="1389054559"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1389255183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1200" b="1"/>
+                  <a:t>Task</a:t>
+                </a:r>
+              </a:p>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1"/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1200" b="1"/>
+                  <a:t>------</a:t>
+                </a:r>
+                <a:br>
+                  <a:rPr lang="en-GB" sz="1200" b="1"/>
+                </a:br>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1200" b="1"/>
+                  <a:t>Model</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1389054559"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1389054559"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1200" b="1"/>
+                  <a:t>Balanced Accuracy</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1200" b="1" baseline="0"/>
+                  <a:t> Mean</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1389255183"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
               <a:rPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000">
@@ -7923,7 +8929,7 @@
               </a:p>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="0"/>
+                  <a:defRPr sz="1200"/>
                 </a:pPr>
                 <a:endParaRPr lang="en-GB" sz="1200" b="0" i="0"/>
               </a:p>
@@ -8045,546 +9051,47 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Irish Dataset:  </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-IE" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0"/>
-              <a:t>Average Improvement Over Random Baseline by Model</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" b="1"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Chart4 - relativeAccuracyModel'!$H$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>avg_relative_improvement</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="bg1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="inEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Chart4 - relativeAccuracyModel'!$G$2:$G$12</c:f>
-              <c:strCache>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>k-NN (k=1)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>k-NN (k=3)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>k-NN (k=5)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>k-NN (k=7)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>k-NN (k=11)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>SVM (RBF Kernel)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Random Forest</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Naive Bayes</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Logistic Regression</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>SVM (Linear)</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Logistic Regression (Weighted)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Chart4 - relativeAccuracyModel'!$H$2:$H$12</c:f>
-              <c:numCache>
-                <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>0.22058773318991201</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.24318918448075769</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.24736137814645034</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.26890001186548718</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.27021457756549483</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.29743821886594501</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.31737390451873354</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.33499851349043003</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.36592986953842538</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.37003461658216513</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.40344671029958601</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C22D-0C45-8A27-A1330C89E94E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="84"/>
-        <c:overlap val="-27"/>
-        <c:axId val="435735456"/>
-        <c:axId val="435670448"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="435735456"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1200"/>
-                  <a:t>Model</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="435670448"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="435670448"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-IE" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
-                  <a:t>Relative Improvement </a:t>
-                </a:r>
-                <a:endParaRPr lang="en-GB" sz="1200"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-GB"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="435735456"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -9449,8 +9956,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -9654,6 +10161,509 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
@@ -12480,7 +13490,7 @@
 </file>
 
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -12985,7 +13995,7 @@
 </file>
 
 <file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -13189,22 +14199,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -13309,8 +14320,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -13442,19 +14453,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -13776,6 +14788,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1397000</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>138546</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>628842</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>125845</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00AEE2B3-11AE-0843-A7B7-15448F7EC3D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>

--- a/FinalReport/Evidence/wav2vec_vs_mfcc/irish_model_summary_charts.xlsx
+++ b/FinalReport/Evidence/wav2vec_vs_mfcc/irish_model_summary_charts.xlsx
@@ -1,30 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cianan/Documents/College/GitHub/FYP/FinalReport/Evidence/wav2vec_vs_mfcc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D20F56B-E86A-574E-9194-3102573DC3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD2844B-F278-A649-B651-87B290A03AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="1360" windowWidth="38400" windowHeight="21800" firstSheet="4" activeTab="8" xr2:uid="{4FF49A69-2F49-B14A-A75D-0C6888D117A2}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21800" activeTab="8" xr2:uid="{4FF49A69-2F49-B14A-A75D-0C6888D117A2}"/>
   </bookViews>
   <sheets>
     <sheet name="irish_model_summary_rebuilt" sheetId="1" r:id="rId1"/>
     <sheet name="Charts" sheetId="2" r:id="rId2"/>
     <sheet name="Chart 1 - dail_only_province" sheetId="3" r:id="rId3"/>
-    <sheet name="Chart 1 - dail_vs_ni" sheetId="4" r:id="rId4"/>
-    <sheet name="Chart 1 - leinster_vs_rest" sheetId="5" r:id="rId5"/>
-    <sheet name="Chart 1 - province_4way" sheetId="6" r:id="rId6"/>
-    <sheet name="Chart 1 - ulster_leinster_rest" sheetId="7" r:id="rId7"/>
+    <sheet name="Chart 1 - province_4way" sheetId="6" r:id="rId4"/>
+    <sheet name="Chart 1 - dail_vs_ni" sheetId="4" r:id="rId5"/>
+    <sheet name="Chart 1 - ulster_leinster_rest" sheetId="7" r:id="rId6"/>
+    <sheet name="Chart 1 - leinster_vs_rest" sheetId="5" r:id="rId7"/>
     <sheet name="Chart 1 - ulster_vs_rest" sheetId="8" r:id="rId8"/>
     <sheet name="Chart 2 - BestModelPerTask" sheetId="9" r:id="rId9"/>
     <sheet name="Chart 3 - AverageAccuracyTask" sheetId="10" r:id="rId10"/>
     <sheet name="Chart4 - relativeAccuracyModel" sheetId="11" r:id="rId11"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId12"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2093,7 +2096,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="18" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2123,6 +2125,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="18" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2168,12 +2171,47 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="108">
+  <dxfs count="156">
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2187,7 +2225,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color auto="1"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2199,126 +2237,13 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
         </left>
         <right style="thin">
           <color theme="0"/>
         </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right/>
         <top style="thin">
           <color theme="0"/>
         </top>
@@ -2339,7 +2264,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color auto="1"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2361,7 +2286,7 @@
           <color theme="0"/>
         </top>
         <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
+          <color theme="0"/>
         </bottom>
         <vertical/>
         <horizontal/>
@@ -2379,43 +2304,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2436,7 +2325,9 @@
         <top style="thin">
           <color theme="0"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -2453,7 +2344,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color auto="1"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2464,36 +2355,44 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
         <top style="thin">
           <color theme="0"/>
         </top>
         <bottom style="thin">
           <color theme="0"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thick">
+        <bottom style="thin">
           <color theme="0"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -2503,7 +2402,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2518,9 +2417,7 @@
         <left style="thin">
           <color theme="0"/>
         </left>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
+        <right/>
         <top/>
         <bottom/>
       </border>
@@ -2562,7 +2459,25 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2579,9 +2494,51 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2621,6 +2578,14 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -2629,7 +2594,23 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2720,6 +2701,38 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -2737,7 +2750,25 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2754,9 +2785,51 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2796,6 +2869,14 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -2804,7 +2885,314 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thick">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2895,6 +3283,38 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -2908,10 +3328,46 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2924,12 +3380,38 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2969,6 +3451,14 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
@@ -2977,7 +3467,312 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thick">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3068,7 +3863,7 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -3076,35 +3871,11 @@
           <color theme="0"/>
         </left>
         <right/>
-        <top/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3141,89 +3912,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thick">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -3240,185 +3928,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thick">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -3490,7 +4004,146 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -3558,7 +4211,7 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -3626,7 +4279,71 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4025,44 +4742,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4076,7 +4755,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color auto="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4088,13 +4767,126 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color theme="0"/>
         </left>
         <right style="thin">
           <color theme="0"/>
         </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
         <top style="thin">
           <color theme="0"/>
         </top>
@@ -4115,7 +4907,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color auto="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4137,7 +4929,7 @@
           <color theme="0"/>
         </top>
         <bottom style="thin">
-          <color theme="0"/>
+          <color theme="4" tint="0.39997558519241921"/>
         </bottom>
         <vertical/>
         <horizontal/>
@@ -4155,7 +4947,43 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4176,9 +5004,7 @@
         <top style="thin">
           <color theme="0"/>
         </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
@@ -4195,7 +5021,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="1"/>
+        <color auto="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -4206,42 +5032,72 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </left>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
+        <right/>
         <top style="thin">
           <color theme="0"/>
         </top>
         <bottom style="thin">
           <color theme="0"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thick">
           <color theme="0"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF215F9A"/>
       <color rgb="FFC1E6F5"/>
       <color rgb="FF83CCEB"/>
     </mruColors>
@@ -5294,935 +6150,6 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="1"/>
-              <a:t>Binary Classification: Dáil vs Northern Ireland</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Chart 1 - dail_vs_ni'!$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>balanced_accuracy_mean</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="tx2">
-                <a:lumMod val="75000"/>
-                <a:lumOff val="25000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="12700">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:alpha val="29000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-3856-6C41-BB88-46F6BA054E2F}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Chart 1 - dail_vs_ni'!$D$2:$D$13</c:f>
-              <c:strCache>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>Random Baseline</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>k-NN (k=11)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>SVM (RBF Kernel)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>k-NN (k=7)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>k-NN (k=1)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>k-NN (k=3)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>k-NN (k=5)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Random Forest</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Logistic Regression</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>SVM (Linear)</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Logistic Regression (Weighted)</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Naive Bayes</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Chart 1 - dail_vs_ni'!$F$2:$F$13</c:f>
-              <c:numCache>
-                <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.65693740471687101</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.65831235479147199</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.65838804078415203</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.66043166910492002</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.668837708052195</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.67095073120098803</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.71707070080305901</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.72374581361208501</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.73857218814408898</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.765450294311946</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.78742267907035202</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3856-6C41-BB88-46F6BA054E2F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="52"/>
-        <c:axId val="1389303087"/>
-        <c:axId val="1388764895"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1389303087"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1388764895"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1388764895"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1200" b="1"/>
-                  <a:t>Balanced</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1200" b="1" baseline="0"/>
-                  <a:t> Accuracy Mean</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-GB" sz="1200" b="1"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-GB"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1389303087"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Irish Dataset:  </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" b="1"/>
-              <a:t>Binary Classification</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" b="1" baseline="0"/>
-              <a:t> -</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" b="1"/>
-              <a:t> Leinster vs Rest</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Chart 1 - leinster_vs_rest'!$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>balanced_accuracy_mean</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="tx2">
-                <a:lumMod val="75000"/>
-                <a:lumOff val="25000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="12700">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:alpha val="29000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-8D9D-2940-B330-69F79082BF47}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Chart 1 - leinster_vs_rest'!$D$2:$D$13</c:f>
-              <c:strCache>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>Random Baseline</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>SVM (RBF Kernel)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Random Forest</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>k-NN (k=1)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>SVM (Linear)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>k-NN (k=3)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Logistic Regression</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>k-NN (k=5)</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>k-NN (k=11)</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>k-NN (k=7)</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Naive Bayes</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Logistic Regression (Weighted)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Chart 1 - leinster_vs_rest'!$F$2:$F$13</c:f>
-              <c:numCache>
-                <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.52132499653409303</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.54934216999991203</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.554791363897845</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.55833869403457703</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.55836682962401596</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.56140121808677201</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.57259215625580095</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.57620999965739295</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.60023140650857298</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.61577722349836606</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-8D9D-2940-B330-69F79082BF47}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="52"/>
-        <c:axId val="1389303087"/>
-        <c:axId val="1388764895"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1389303087"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1388764895"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1388764895"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Balanced Accuracy Mean</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1389303087"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
               <a:rPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000">
@@ -6664,7 +6591,461 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Binary Classification: Dáil vs Northern Ireland</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Chart 1 - dail_vs_ni'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>balanced_accuracy_mean</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:alpha val="29000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-3856-6C41-BB88-46F6BA054E2F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Chart 1 - dail_vs_ni'!$D$2:$D$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Random Baseline</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>k-NN (k=11)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SVM (RBF Kernel)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>k-NN (k=7)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>k-NN (k=1)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>k-NN (k=3)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>k-NN (k=5)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Random Forest</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Logistic Regression</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>SVM (Linear)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Logistic Regression (Weighted)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Naive Bayes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Chart 1 - dail_vs_ni'!$F$2:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.65693740471687101</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.65831235479147199</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.65838804078415203</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.66043166910492002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.668837708052195</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.67095073120098803</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.71707070080305901</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.72374581361208501</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.73857218814408898</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.765450294311946</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.78742267907035202</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3856-6C41-BB88-46F6BA054E2F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="52"/>
+        <c:axId val="1389303087"/>
+        <c:axId val="1388764895"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1389303087"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1388764895"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1388764895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1200" b="1"/>
+                  <a:t>Balanced</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1200" b="1" baseline="0"/>
+                  <a:t> Accuracy Mean</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB" sz="1200" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-GB"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1389303087"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -6811,6 +7192,27 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="215F9A"/>
+              </a:solidFill>
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-9F1B-7B4D-8BCD-2EC66216F8B4}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:cat>
             <c:strRef>
               <c:f>'Chart 1 - ulster_leinster_rest'!$D$2:$D$13</c:f>
@@ -6903,6 +7305,481 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-9E8C-E849-B90B-2B880992402A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="52"/>
+        <c:axId val="1389303087"/>
+        <c:axId val="1388764895"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1389303087"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1388764895"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1388764895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Balanced Accuracy Mean</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1389303087"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Irish Dataset:  </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Binary Classification</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:t> -</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t> Leinster vs Rest</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Chart 1 - leinster_vs_rest'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>balanced_accuracy_mean</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="12700">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:alpha val="29000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-8D9D-2940-B330-69F79082BF47}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Chart 1 - leinster_vs_rest'!$D$2:$D$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Random Baseline</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SVM (RBF Kernel)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Random Forest</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>k-NN (k=1)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>SVM (Linear)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>k-NN (k=3)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Logistic Regression</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>k-NN (k=5)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>k-NN (k=11)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>k-NN (k=7)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Naive Bayes</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Logistic Regression (Weighted)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Chart 1 - leinster_vs_rest'!$F$2:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.52132499653409303</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.54934216999991203</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.554791363897845</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.55833869403457703</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.55836682962401596</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.56140121808677201</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.57259215625580095</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.57620999965739295</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.60023140650857298</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.61577722349836606</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8D9D-2940-B330-69F79082BF47}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7728,28 +8605,28 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Dáil Speakers
-Logistic Regression</c:v>
+                  <c:v>Four Provinces
+SVM (Linear)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Four Provinces
-SVM (Linear)</c:v>
+                  <c:v>Dáil vs Northern Ireland
+Naive Bayes</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Ulster, Leinster, and Rest
 SVM (RBF Kernel)</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>Ulster vs Rest
+Logistic Regression (Weighted)</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Leinster vs Rest
 Logistic Regression (Weighted)</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>Ulster vs Rest
-Logistic Regression (Weighted)</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>Dáil vs Northern Ireland
-Naive Bayes</c:v>
+                  <c:v>Dáil Speakers
+Logistic Regression</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7761,22 +8638,22 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.27210886725816702</c:v>
+                  <c:v>0.39387690904640299</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.39387690904640299</c:v>
+                  <c:v>0.78742267907035202</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.52408969936051997</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>0.74775796701111596</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>0.61580000000000001</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.74775796701111596</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.78742267907035202</c:v>
+                  <c:v>0.27210886725816702</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8116,14 +8993,6 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" b="1"/>
-              <a:t>Irish</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" b="1" baseline="0"/>
-              <a:t> Dataset: </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" b="1"/>
               <a:t>Best Model Per Task</a:t>
             </a:r>
           </a:p>
@@ -8137,26 +9006,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -8166,7 +9015,7 @@
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
@@ -8181,76 +9030,110 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="0070C0"/>
+              <a:srgbClr val="215F9A"/>
             </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Chart 2 - BestModelPerTask'!$F$2:$F$7</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Dáil Speakers
-Logistic Regression</c:v>
+                  <c:v>Four Provinces
+SVM (Linear)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Four Provinces
-SVM (Linear)</c:v>
+                  <c:v>Dáil vs Northern Ireland
+Naive Bayes</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Ulster, Leinster, and Rest
 SVM (RBF Kernel)</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>Ulster vs Rest
+Logistic Regression (Weighted)</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Leinster vs Rest
 Logistic Regression (Weighted)</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>Ulster vs Rest
-Logistic Regression (Weighted)</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>Dáil vs Northern Ireland
-Naive Bayes</c:v>
+                  <c:v>Dáil Speakers
+Logistic Regression</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Chart 2 - BestModelPerTask'!$G$2:$G$7</c:f>
+              <c:f>'Chart 2 - BestModelPerTask'!$J$2:$J$7</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.27210886725816702</c:v>
+                  <c:v>0.57550763618561196</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.39387690904640299</c:v>
+                  <c:v>0.57484535814070403</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.52408969936051997</c:v>
+                  <c:v>0.57242634071563159</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.61580000000000001</c:v>
+                  <c:v>0.49551593402223193</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.74775796701111596</c:v>
+                  <c:v>0.23160000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.78742267907035202</c:v>
+                  <c:v>8.8435469032668079E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FC17-C142-8CB0-BC342651D6BF}"/>
+              <c16:uniqueId val="{00000003-0A05-E949-A1BA-124911998138}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8262,12 +9145,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="50"/>
-        <c:axId val="1389255183"/>
-        <c:axId val="1389054559"/>
+        <c:gapWidth val="119"/>
+        <c:overlap val="-9"/>
+        <c:axId val="91009679"/>
+        <c:axId val="91011391"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1389255183"/>
+        <c:axId val="91009679"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8280,7 +9164,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -8293,23 +9177,21 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-GB" sz="1200" b="1"/>
+                  <a:rPr lang="en-GB" sz="1050"/>
                   <a:t>Task</a:t>
                 </a:r>
-              </a:p>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="1"/>
-                </a:pPr>
+                <a:br>
+                  <a:rPr lang="en-GB" sz="1050"/>
+                </a:br>
                 <a:r>
-                  <a:rPr lang="en-GB" sz="1200" b="1"/>
-                  <a:t>------</a:t>
+                  <a:rPr lang="en-GB" sz="1050"/>
+                  <a:t>-------</a:t>
                 </a:r>
                 <a:br>
-                  <a:rPr lang="en-GB" sz="1200" b="1"/>
+                  <a:rPr lang="en-GB" sz="1050"/>
                 </a:br>
                 <a:r>
-                  <a:rPr lang="en-GB" sz="1200" b="1"/>
+                  <a:rPr lang="en-GB" sz="1050"/>
                   <a:t>Model</a:t>
                 </a:r>
               </a:p>
@@ -8323,26 +9205,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -8362,11 +9224,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="0"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -8381,7 +9243,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1389054559"/>
+        <c:crossAx val="91011391"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8389,7 +9251,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1389054559"/>
+        <c:axId val="91011391"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8416,7 +9278,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -8429,12 +9291,15 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-GB" sz="1200" b="1"/>
-                  <a:t>Balanced Accuracy</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1200" b="1" baseline="0"/>
-                  <a:t> Mean</a:t>
+                  <a:rPr lang="en-GB" sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Relative Improvement Over the Baseline</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -8447,26 +9312,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -8499,37 +9344,15 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1389255183"/>
+        <c:crossAx val="91009679"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
@@ -9091,46 +9914,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -9956,8 +10739,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -10161,22 +10944,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -10281,8 +11065,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -10414,19 +11198,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -10459,7 +11244,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -10964,7 +11749,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11469,7 +12254,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11974,7 +12759,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -12479,7 +13264,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -12984,8 +13769,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -13489,8 +14274,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -13694,23 +14479,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -13815,8 +14599,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -13948,525 +14732,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -14504,15 +14782,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>241398</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>84666</xdr:rowOff>
+      <xdr:colOff>347231</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>116416</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>759883</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>71967</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>40216</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>103717</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14545,15 +14823,58 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>42334</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>127001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>584102</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>124884</xdr:rowOff>
+      <xdr:colOff>194636</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>50801</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EBF6A56-8F4B-C841-99BD-A3F240E044F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>10584</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>169333</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>594686</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>93134</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14583,70 +14904,27 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>719569</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>188384</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1041302</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>124884</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12C6AA8B-E3D1-5249-81D8-48156A15C31A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>152302</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EBF6A56-8F4B-C841-99BD-A3F240E044F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3AA030C-6309-5D4D-B8F6-85206C60497B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14675,21 +14953,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1041302</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>124884</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>719569</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3AA030C-6309-5D4D-B8F6-85206C60497B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12C6AA8B-E3D1-5249-81D8-48156A15C31A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14796,22 +15074,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1397000</xdr:colOff>
+      <xdr:colOff>1616363</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>138546</xdr:rowOff>
+      <xdr:rowOff>11545</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>628842</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>125845</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>206663</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00AEE2B3-11AE-0843-A7B7-15448F7EC3D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{855D1014-6E9E-3C45-BB7D-E2E5D8FFA211}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14916,13 +15194,81 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="wav2vec_irish_summary"/>
+      <sheetName val="Chart 1 - B.A. per Task"/>
+      <sheetName val="Chart 2 - F1 per Task"/>
+      <sheetName val=" Chart 3 — Accuracy vs Balanced"/>
+      <sheetName val="Chart 4 - Average B.A. Per Task"/>
+      <sheetName val="Chart 5 - Best Model Per Task"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5">
+        <row r="1">
+          <cell r="Q1" t="str">
+            <v>RelativeImprovement</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="E2" t="str">
+            <v>Leinster vs Rest
+Logistic Regression (Weighted)</v>
+          </cell>
+          <cell r="Q2">
+            <v>0.36192950984118011</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="E3" t="str">
+            <v>Ulster vs Rest
+Random Forest</v>
+          </cell>
+          <cell r="Q3">
+            <v>0.56875046258539808</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="E4" t="str">
+            <v xml:space="preserve">Ulster, Leinster, and Rest
+Logistic Regression </v>
+          </cell>
+          <cell r="Q4">
+            <v>0.79009262318694806</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="E5" t="str">
+            <v xml:space="preserve">Four Provinces
+Logistic Regression </v>
+          </cell>
+          <cell r="Q5">
+            <v>0.86392249287122391</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EE58ED0B-2560-9848-955A-052EBF2D7125}" name="Table1" displayName="Table1" ref="A1:N67" totalsRowShown="0">
   <autoFilter ref="A1:N67" xr:uid="{EE58ED0B-2560-9848-955A-052EBF2D7125}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{24865EAA-300E-E845-879E-C8D6CBA13050}" name="task_name"/>
     <tableColumn id="2" xr3:uid="{978F9106-1277-754C-A4F2-4BAAB7CB2E3D}" name="model_name"/>
-    <tableColumn id="14" xr3:uid="{478F359E-30CB-AE4B-B851-462D1CC2BA02}" name="task_model" dataDxfId="96">
+    <tableColumn id="14" xr3:uid="{478F359E-30CB-AE4B-B851-462D1CC2BA02}" name="task_model" dataDxfId="143">
       <calculatedColumnFormula>_xlfn.CONCAT(Table1[[#This Row],[task_name]]," -  ",Table1[[#This Row],[model_name]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{ACF67C75-2B67-F64B-AFB6-261BC81C2550}" name="n_samples"/>
@@ -14934,10 +15280,10 @@
     <tableColumn id="9" xr3:uid="{FCFFC612-1875-F046-A939-4E7655977CC7}" name="accuracy_std"/>
     <tableColumn id="10" xr3:uid="{CD6CF502-A09B-8248-8F0C-565A06FF3F86}" name="balanced_accuracy_mean"/>
     <tableColumn id="11" xr3:uid="{601027DF-067B-7A4C-8A82-198B0346FE08}" name="macro_f1_mean"/>
-    <tableColumn id="12" xr3:uid="{AEEEFE73-6E0B-854E-A2E5-8BEFBF35FB8C}" name="Baseline" dataDxfId="95">
+    <tableColumn id="12" xr3:uid="{AEEEFE73-6E0B-854E-A2E5-8BEFBF35FB8C}" name="Baseline" dataDxfId="142">
       <calculatedColumnFormula>1/Table1[[#This Row],[n_classes]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{4B4C074C-4EED-7B42-AA4B-8337CEDD1F96}" name="relative_improvement" dataDxfId="94">
+    <tableColumn id="15" xr3:uid="{4B4C074C-4EED-7B42-AA4B-8337CEDD1F96}" name="relative_improvement" dataDxfId="141">
       <calculatedColumnFormula>(Table1[[#This Row],[balanced_accuracy_mean]]-Table1[[#This Row],[Baseline]])/Table1[[#This Row],[Baseline]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14953,35 +15299,35 @@
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{B6851B0E-C81C-9342-A50C-09E9F1869D61}" name="task_name"/>
-    <tableColumn id="2" xr3:uid="{A77C3616-7FB4-134F-84FC-F909C19EBF75}" name="avg_accuracy" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{A77C3616-7FB4-134F-84FC-F909C19EBF75}" name="avg_accuracy" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{42D48207-C6A6-B04D-8EB3-9C101B72CDA6}" name="Table18" displayName="Table18" ref="A1:D67" totalsRowShown="0" headerRowDxfId="107" tableBorderDxfId="106">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{42D48207-C6A6-B04D-8EB3-9C101B72CDA6}" name="Table18" displayName="Table18" ref="A1:D67" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="A1:D67" xr:uid="{42D48207-C6A6-B04D-8EB3-9C101B72CDA6}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3AECEAF4-D21F-404D-B8EE-F07B62D89BAD}" name="task_name" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{29BCF6A8-6B27-E649-A01C-C672CC42A309}" name="model_name" dataDxfId="104"/>
-    <tableColumn id="3" xr3:uid="{D9C2E662-0375-8348-B4F3-6AC19DBC13CC}" name="task_model" dataDxfId="103"/>
-    <tableColumn id="4" xr3:uid="{1EA0313A-4D90-904E-A9EA-3371651E833A}" name="balanced_accuracy_mean" dataDxfId="102"/>
+    <tableColumn id="1" xr3:uid="{3AECEAF4-D21F-404D-B8EE-F07B62D89BAD}" name="task_name" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{29BCF6A8-6B27-E649-A01C-C672CC42A309}" name="model_name" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{D9C2E662-0375-8348-B4F3-6AC19DBC13CC}" name="task_model" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{1EA0313A-4D90-904E-A9EA-3371651E833A}" name="balanced_accuracy_mean" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9F5FB4A-A0FD-804F-9CCC-C6778240EA4A}" name="Table3" displayName="Table3" ref="F1:H12" totalsRowShown="0" headerRowDxfId="101" dataDxfId="100">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F9F5FB4A-A0FD-804F-9CCC-C6778240EA4A}" name="Table3" displayName="Table3" ref="F1:H12" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="F1:H12" xr:uid="{F9F5FB4A-A0FD-804F-9CCC-C6778240EA4A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F2:H12">
     <sortCondition ref="H1:H12"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{99B910B8-21EF-4A44-B5DF-9330EAD68E65}" name="model_name" dataDxfId="99"/>
-    <tableColumn id="2" xr3:uid="{6B05F421-F98E-EC45-B423-8B2ECCA65FC4}" name="model_name_better" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{B0652A93-BFFA-0048-A590-459A6FB9D430}" name="avg_relative_improvement" dataDxfId="97">
+    <tableColumn id="1" xr3:uid="{99B910B8-21EF-4A44-B5DF-9330EAD68E65}" name="model_name" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{6B05F421-F98E-EC45-B423-8B2ECCA65FC4}" name="model_name_better" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{B0652A93-BFFA-0048-A590-459A6FB9D430}" name="avg_relative_improvement" dataDxfId="0">
       <calculatedColumnFormula>AVERAGEIF(irish_model_summary_rebuilt!B:B, F2, irish_model_summary_rebuilt!N:N)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -14990,7 +15336,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E2C532A2-EF49-1E42-A3BE-DD330163513E}" name="Table2" displayName="Table2" ref="A1:E67" totalsRowShown="0" headerRowDxfId="93" dataDxfId="91" headerRowBorderDxfId="92" tableBorderDxfId="90" totalsRowBorderDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E2C532A2-EF49-1E42-A3BE-DD330163513E}" name="Table2" displayName="Table2" ref="A1:E67" totalsRowShown="0" headerRowDxfId="140" dataDxfId="138" headerRowBorderDxfId="139" tableBorderDxfId="137" totalsRowBorderDxfId="136">
   <autoFilter ref="A1:E67" xr:uid="{E2C532A2-EF49-1E42-A3BE-DD330163513E}">
     <filterColumn colId="1">
       <filters>
@@ -14999,161 +15345,185 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{142B9034-2955-9240-A916-974FAFB7EF2C}" name="task_name" dataDxfId="88"/>
-    <tableColumn id="2" xr3:uid="{8B35E1A6-2D38-C54D-8AB2-86FF5B0F94A6}" name="model_name" dataDxfId="87"/>
-    <tableColumn id="3" xr3:uid="{16A2A86C-629A-2A42-A36C-5A1E089A96E6}" name="task_model" dataDxfId="86"/>
-    <tableColumn id="4" xr3:uid="{47A1107B-D709-334E-AFE9-03A1E3925A7C}" name="balanced_accuracy_mean" dataDxfId="85"/>
-    <tableColumn id="5" xr3:uid="{1C2E424D-0081-2643-BCFF-4B3D30129152}" name="macro_f1_mean" dataDxfId="84"/>
+    <tableColumn id="1" xr3:uid="{142B9034-2955-9240-A916-974FAFB7EF2C}" name="task_name" dataDxfId="135"/>
+    <tableColumn id="2" xr3:uid="{8B35E1A6-2D38-C54D-8AB2-86FF5B0F94A6}" name="model_name" dataDxfId="134"/>
+    <tableColumn id="3" xr3:uid="{16A2A86C-629A-2A42-A36C-5A1E089A96E6}" name="task_model" dataDxfId="133"/>
+    <tableColumn id="4" xr3:uid="{47A1107B-D709-334E-AFE9-03A1E3925A7C}" name="balanced_accuracy_mean" dataDxfId="132"/>
+    <tableColumn id="5" xr3:uid="{1C2E424D-0081-2643-BCFF-4B3D30129152}" name="macro_f1_mean" dataDxfId="131"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7A76E0F9-7107-3946-AC4D-87A384DFDAE8}" name="Table5" displayName="Table5" ref="A1:H13" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82" tableBorderDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7A76E0F9-7107-3946-AC4D-87A384DFDAE8}" name="Table5" displayName="Table5" ref="A1:H14" totalsRowCount="1" headerRowDxfId="130" dataDxfId="129" tableBorderDxfId="128">
   <autoFilter ref="A1:H13" xr:uid="{7A76E0F9-7107-3946-AC4D-87A384DFDAE8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H13">
     <sortCondition descending="1" ref="H2:H13"/>
     <sortCondition ref="F2:F13"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{AAD35B54-3EAF-6E40-8617-8A0ECD5075DC}" name="task_name" dataDxfId="80"/>
-    <tableColumn id="9" xr3:uid="{C9F33185-E1B2-9D48-B45E-0E1AC11D32F1}" name="task_name_better" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{68FCD6E5-29EB-1E47-ADD3-2FC338197480}" name="model_name" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{17D8DDF7-E573-6F4A-A2EA-56F88B99217B}" name="model_name_better" dataDxfId="77"/>
-    <tableColumn id="4" xr3:uid="{9662570C-4A72-F048-8782-78E3DF93F8E0}" name="task_model" dataDxfId="76"/>
-    <tableColumn id="5" xr3:uid="{A4D12154-4241-CB40-B349-6C6610111267}" name="balanced_accuracy_mean" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{1686227E-110F-B146-AA28-082FBD18F701}" name="macro_f1_mean" dataDxfId="74"/>
-    <tableColumn id="8" xr3:uid="{DBD9411C-6602-3E49-B449-61CFD7D6EEDA}" name="signal_flag" dataDxfId="73"/>
+    <tableColumn id="1" xr3:uid="{AAD35B54-3EAF-6E40-8617-8A0ECD5075DC}" name="task_name" dataDxfId="127" totalsRowDxfId="126"/>
+    <tableColumn id="9" xr3:uid="{C9F33185-E1B2-9D48-B45E-0E1AC11D32F1}" name="task_name_better" dataDxfId="125" totalsRowDxfId="124"/>
+    <tableColumn id="2" xr3:uid="{68FCD6E5-29EB-1E47-ADD3-2FC338197480}" name="model_name" dataDxfId="123" totalsRowDxfId="122"/>
+    <tableColumn id="3" xr3:uid="{17D8DDF7-E573-6F4A-A2EA-56F88B99217B}" name="model_name_better" dataDxfId="121" totalsRowDxfId="120"/>
+    <tableColumn id="4" xr3:uid="{9662570C-4A72-F048-8782-78E3DF93F8E0}" name="task_model" dataDxfId="119" totalsRowDxfId="118"/>
+    <tableColumn id="5" xr3:uid="{A4D12154-4241-CB40-B349-6C6610111267}" name="balanced_accuracy_mean" totalsRowFunction="custom" dataDxfId="117" totalsRowDxfId="116">
+      <totalsRowFormula>AVERAGE(F3:F13)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{1686227E-110F-B146-AA28-082FBD18F701}" name="macro_f1_mean" totalsRowFunction="custom" dataDxfId="115" totalsRowDxfId="114">
+      <totalsRowFormula>AVERAGE(G3:G13)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{DBD9411C-6602-3E49-B449-61CFD7D6EEDA}" name="signal_flag" dataDxfId="113" totalsRowDxfId="112"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C6A3EF97-7678-EC45-B888-F29C82D60E08}" name="Table11" displayName="Table11" ref="A1:H13" totalsRowShown="0" headerRowDxfId="72" dataDxfId="70" headerRowBorderDxfId="71" tableBorderDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{F9AB2B87-6486-D14C-948E-3F06D4FADBEC}" name="Table13" displayName="Table13" ref="A1:H14" totalsRowCount="1" headerRowDxfId="111" dataDxfId="109" headerRowBorderDxfId="110" tableBorderDxfId="108">
+  <autoFilter ref="A1:H13" xr:uid="{F9AB2B87-6486-D14C-948E-3F06D4FADBEC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H13">
+    <sortCondition descending="1" ref="H2:H13"/>
+    <sortCondition ref="F2:F13"/>
+  </sortState>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{6374312C-890B-DA42-A7FA-6FC172E5A626}" name="task_name" dataDxfId="107" totalsRowDxfId="106"/>
+    <tableColumn id="8" xr3:uid="{073317FD-1436-5541-9416-0C42F0B37258}" name="task_name_better" dataDxfId="105" totalsRowDxfId="104"/>
+    <tableColumn id="2" xr3:uid="{5CAAEA7F-3B0C-3944-920A-EE74BAE561E7}" name="model_name" dataDxfId="103" totalsRowDxfId="102"/>
+    <tableColumn id="6" xr3:uid="{8FB6C0CF-CF22-4C45-A05F-4379E28286B7}" name="model_name_better" dataDxfId="101" totalsRowDxfId="100"/>
+    <tableColumn id="3" xr3:uid="{5380910C-857C-5B41-AE4D-24EB552A4BEC}" name="task_model" dataDxfId="99" totalsRowDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{97DF686C-F9F6-684C-BF5A-07095A2647BE}" name="balanced_accuracy_mean" totalsRowFunction="custom" dataDxfId="97" totalsRowDxfId="96">
+      <totalsRowFormula>AVERAGE(F3:F13)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{025D0624-AD00-9447-9D53-DC5AEAEAB0F6}" name="macro_f1_mean" totalsRowFunction="custom" dataDxfId="95" totalsRowDxfId="94">
+      <totalsRowFormula>AVERAGE(G3:G13)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{E181C427-8718-B044-925B-6FE7D718EF3C}" name="signal_flag" dataDxfId="93" totalsRowDxfId="92"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C6A3EF97-7678-EC45-B888-F29C82D60E08}" name="Table11" displayName="Table11" ref="A1:H14" totalsRowCount="1" headerRowDxfId="91" dataDxfId="89" headerRowBorderDxfId="90" tableBorderDxfId="88">
   <autoFilter ref="A1:H13" xr:uid="{C6A3EF97-7678-EC45-B888-F29C82D60E08}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H13">
     <sortCondition descending="1" ref="H2:H13"/>
     <sortCondition ref="F2:F13"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{E5882BA5-E78D-284C-B53C-617E67918292}" name="task_name" dataDxfId="68"/>
-    <tableColumn id="8" xr3:uid="{45B661FC-63B8-1845-93E2-12EF8CAE6ACE}" name="task_name_better" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{5002A805-AA98-214D-BB5B-A6BC1C1F2CAB}" name="model_name" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{3C6430D2-FCB4-E345-BCFE-161922E6079C}" name="model_name_better" dataDxfId="65"/>
-    <tableColumn id="3" xr3:uid="{3452F9E3-A4DF-BA43-A2DD-29179CE42E65}" name="task_model" dataDxfId="64"/>
-    <tableColumn id="4" xr3:uid="{F292781B-F869-134C-8774-214D7580F1C5}" name="balanced_accuracy_mean" dataDxfId="63"/>
-    <tableColumn id="5" xr3:uid="{2CA5D4C4-4E8F-5F4A-85E0-FEDF61F4D206}" name="macro_f1_mean" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{85A1BB48-02DA-704F-8075-66875844867B}" name="signal_flag" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{E5882BA5-E78D-284C-B53C-617E67918292}" name="task_name" dataDxfId="87" totalsRowDxfId="86"/>
+    <tableColumn id="8" xr3:uid="{45B661FC-63B8-1845-93E2-12EF8CAE6ACE}" name="task_name_better" dataDxfId="85" totalsRowDxfId="84"/>
+    <tableColumn id="2" xr3:uid="{5002A805-AA98-214D-BB5B-A6BC1C1F2CAB}" name="model_name" dataDxfId="83" totalsRowDxfId="82"/>
+    <tableColumn id="6" xr3:uid="{3C6430D2-FCB4-E345-BCFE-161922E6079C}" name="model_name_better" dataDxfId="81" totalsRowDxfId="80"/>
+    <tableColumn id="3" xr3:uid="{3452F9E3-A4DF-BA43-A2DD-29179CE42E65}" name="task_model" dataDxfId="79" totalsRowDxfId="78"/>
+    <tableColumn id="4" xr3:uid="{F292781B-F869-134C-8774-214D7580F1C5}" name="balanced_accuracy_mean" totalsRowFunction="custom" dataDxfId="77" totalsRowDxfId="76">
+      <totalsRowFormula>AVERAGE(F3:F13)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{2CA5D4C4-4E8F-5F4A-85E0-FEDF61F4D206}" name="macro_f1_mean" totalsRowFunction="custom" dataDxfId="75" totalsRowDxfId="74">
+      <totalsRowFormula>AVERAGE(G3:G13)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{85A1BB48-02DA-704F-8075-66875844867B}" name="signal_flag" dataDxfId="73" totalsRowDxfId="72"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{3B780881-C7BE-A34D-9B17-043E1CEF2FAD}" name="Table12" displayName="Table12" ref="A1:H13" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{B2712CC1-E9AE-AC4E-A627-90534361CF1C}" name="Table14" displayName="Table14" ref="A1:H14" totalsRowCount="1" headerRowDxfId="71" dataDxfId="69" headerRowBorderDxfId="70" tableBorderDxfId="68">
+  <autoFilter ref="A1:H13" xr:uid="{B2712CC1-E9AE-AC4E-A627-90534361CF1C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H13">
+    <sortCondition descending="1" ref="H2:H13"/>
+    <sortCondition ref="F2:F13"/>
+  </sortState>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{02D8805E-0A7C-CF42-8A80-589C337723C1}" name="task_name" dataDxfId="67" totalsRowDxfId="66"/>
+    <tableColumn id="8" xr3:uid="{069BC9A1-6D50-9249-8850-E243D02C4362}" name="task_name_better" dataDxfId="65" totalsRowDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{5231E99D-D48C-604A-9835-33D03D991497}" name="model_name" dataDxfId="63" totalsRowDxfId="62"/>
+    <tableColumn id="6" xr3:uid="{757B3F5B-0BC5-7D42-8C4A-845409FC5AEA}" name="model_name_better" dataDxfId="61" totalsRowDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{8C41849B-7CDC-284C-A25D-BACECCA7F7A0}" name="task_model" dataDxfId="59" totalsRowDxfId="58"/>
+    <tableColumn id="4" xr3:uid="{B3B59721-D85F-654A-8224-AF277D146F97}" name="balanced_accuracy_mean" totalsRowFunction="custom" dataDxfId="57" totalsRowDxfId="56">
+      <totalsRowFormula>AVERAGE(F3:F13)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{2DD913F8-93F2-E947-A6FE-057B75C6A0D7}" name="macro_f1_mean" totalsRowFunction="custom" dataDxfId="55" totalsRowDxfId="54">
+      <totalsRowFormula>AVERAGE(G3:G13)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{BE128D2F-7A40-7F42-A8D7-CE3A1D443E57}" name="signal_flag" dataDxfId="53" totalsRowDxfId="52"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{3B780881-C7BE-A34D-9B17-043E1CEF2FAD}" name="Table12" displayName="Table12" ref="A1:H14" totalsRowCount="1" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48">
   <autoFilter ref="A1:H13" xr:uid="{3B780881-C7BE-A34D-9B17-043E1CEF2FAD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H13">
     <sortCondition descending="1" ref="H2:H13"/>
     <sortCondition ref="F2:F13"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{A4A74DF5-8878-0D48-BE94-CA22270B30C5}" name="task_name" dataDxfId="56"/>
-    <tableColumn id="8" xr3:uid="{643B6BCF-F669-8E4B-9563-CA11B11B03B5}" name="task_name_better" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{473904A9-7DE0-6F42-82AC-5104C91C9CB1}" name="model_name" dataDxfId="54"/>
-    <tableColumn id="6" xr3:uid="{08277F9E-74F2-5441-9ACD-DBFE622BAD34}" name="model_name_better" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{CB99A8CF-B5F6-8944-A79E-DFF38F5ED746}" name="task_model" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{68D5A583-61E4-B244-9682-9B1E6B5DE842}" name="balanced_accuracy_mean" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{0197EA97-6BF1-2F4F-973B-58804D92FF87}" name="macro_f1_mean" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{4E0C1201-B933-5F4C-9D08-10837A441436}" name="signal_flag" dataDxfId="49"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{F9AB2B87-6486-D14C-948E-3F06D4FADBEC}" name="Table13" displayName="Table13" ref="A1:H13" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45">
-  <autoFilter ref="A1:H13" xr:uid="{F9AB2B87-6486-D14C-948E-3F06D4FADBEC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H13">
-    <sortCondition descending="1" ref="H2:H13"/>
-    <sortCondition ref="F2:F13"/>
-  </sortState>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{6374312C-890B-DA42-A7FA-6FC172E5A626}" name="task_name" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{073317FD-1436-5541-9416-0C42F0B37258}" name="task_name_better" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{5CAAEA7F-3B0C-3944-920A-EE74BAE561E7}" name="model_name" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{8FB6C0CF-CF22-4C45-A05F-4379E28286B7}" name="model_name_better" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{5380910C-857C-5B41-AE4D-24EB552A4BEC}" name="task_model" dataDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{97DF686C-F9F6-684C-BF5A-07095A2647BE}" name="balanced_accuracy_mean" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{025D0624-AD00-9447-9D53-DC5AEAEAB0F6}" name="macro_f1_mean" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{E181C427-8718-B044-925B-6FE7D718EF3C}" name="signal_flag" dataDxfId="37"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{B2712CC1-E9AE-AC4E-A627-90534361CF1C}" name="Table14" displayName="Table14" ref="A1:H13" totalsRowShown="0" headerRowDxfId="36" dataDxfId="34" headerRowBorderDxfId="35" tableBorderDxfId="33">
-  <autoFilter ref="A1:H13" xr:uid="{B2712CC1-E9AE-AC4E-A627-90534361CF1C}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H13">
-    <sortCondition descending="1" ref="H2:H13"/>
-    <sortCondition ref="F2:F13"/>
-  </sortState>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{02D8805E-0A7C-CF42-8A80-589C337723C1}" name="task_name" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{069BC9A1-6D50-9249-8850-E243D02C4362}" name="task_name_better" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{5231E99D-D48C-604A-9835-33D03D991497}" name="model_name" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{757B3F5B-0BC5-7D42-8C4A-845409FC5AEA}" name="model_name_better" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{8C41849B-7CDC-284C-A25D-BACECCA7F7A0}" name="task_model" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{B3B59721-D85F-654A-8224-AF277D146F97}" name="balanced_accuracy_mean" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{2DD913F8-93F2-E947-A6FE-057B75C6A0D7}" name="macro_f1_mean" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{BE128D2F-7A40-7F42-A8D7-CE3A1D443E57}" name="signal_flag" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{A4A74DF5-8878-0D48-BE94-CA22270B30C5}" name="task_name" dataDxfId="47" totalsRowDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{643B6BCF-F669-8E4B-9563-CA11B11B03B5}" name="task_name_better" dataDxfId="45" totalsRowDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{473904A9-7DE0-6F42-82AC-5104C91C9CB1}" name="model_name" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{08277F9E-74F2-5441-9ACD-DBFE622BAD34}" name="model_name_better" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{CB99A8CF-B5F6-8944-A79E-DFF38F5ED746}" name="task_model" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{68D5A583-61E4-B244-9682-9B1E6B5DE842}" name="balanced_accuracy_mean" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="36">
+      <totalsRowFormula>AVERAGE(F3:F13)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{0197EA97-6BF1-2F4F-973B-58804D92FF87}" name="macro_f1_mean" totalsRowFunction="custom" dataDxfId="35" totalsRowDxfId="34">
+      <totalsRowFormula>AVERAGE(G3:G13)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{4E0C1201-B933-5F4C-9D08-10837A441436}" name="signal_flag" dataDxfId="33" totalsRowDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{271D6F7D-1C6A-F64B-A428-386D6E344ABD}" name="Table15" displayName="Table15" ref="A1:H13" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{271D6F7D-1C6A-F64B-A428-386D6E344ABD}" name="Table15" displayName="Table15" ref="A1:H14" totalsRowCount="1" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28">
   <autoFilter ref="A1:H13" xr:uid="{271D6F7D-1C6A-F64B-A428-386D6E344ABD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H13">
     <sortCondition descending="1" ref="H2:H13"/>
     <sortCondition ref="F2:F13"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{E6C8AA3D-BA72-4E49-8A2F-1FA13FDCD217}" name="task_name" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{808B8353-6E8E-7043-BCD5-3D4237C51963}" name="task_name_better" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{4AE861CA-2C44-E040-A780-66F227D793C9}" name="model_name" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{5DE88E96-2539-7443-8A1D-C53581F5783D}" name="model_name_better" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{A1761733-9D2B-E841-A02A-2694BB96FD6E}" name="task_model" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{202D40AD-E12E-744C-8EA0-80CCD8490A34}" name="balanced_accuracy_mean" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{5CDFB833-42D7-5743-8544-FA94307CBD30}" name="macro_f1_mean" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{371CD96D-B44F-E44A-AF19-3A1E71220A16}" name="signal_flag" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{E6C8AA3D-BA72-4E49-8A2F-1FA13FDCD217}" name="task_name" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{808B8353-6E8E-7043-BCD5-3D4237C51963}" name="task_name_better" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{4AE861CA-2C44-E040-A780-66F227D793C9}" name="model_name" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{5DE88E96-2539-7443-8A1D-C53581F5783D}" name="model_name_better" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{A1761733-9D2B-E841-A02A-2694BB96FD6E}" name="task_model" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{202D40AD-E12E-744C-8EA0-80CCD8490A34}" name="balanced_accuracy_mean" totalsRowFunction="custom" dataDxfId="17" totalsRowDxfId="16">
+      <totalsRowFormula>AVERAGE(F3:F13)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{5CDFB833-42D7-5743-8544-FA94307CBD30}" name="macro_f1_mean" totalsRowFunction="custom" dataDxfId="15" totalsRowDxfId="14">
+      <totalsRowFormula>AVERAGE(G3:G13)</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{371CD96D-B44F-E44A-AF19-3A1E71220A16}" name="signal_flag" dataDxfId="13" totalsRowDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C527B775-C7A6-BC4F-B663-B946EA212D18}" name="Table16" displayName="Table16" ref="A1:J7" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{C527B775-C7A6-BC4F-B663-B946EA212D18}" name="Table16" displayName="Table16" ref="A1:J7" totalsRowShown="0" headerRowDxfId="155" headerRowBorderDxfId="154" tableBorderDxfId="153">
   <autoFilter ref="A1:J7" xr:uid="{C527B775-C7A6-BC4F-B663-B946EA212D18}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H7">
-    <sortCondition ref="G1:G7"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J7">
+    <sortCondition descending="1" ref="J1:J7"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9ED5B514-B946-0E46-8CC4-65EB2916205D}" name="task_name" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{6A16E901-5BDC-D444-B622-2DE255771BB6}" name="task_name_better" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{851E4485-7C38-814F-9C47-82F349076D30}" name="model_name" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{24C3B122-2693-FC4A-B315-868DA09E553F}" name="model_name_better" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{04A3ECDA-65E9-9147-AE27-A3673EA119E3}" name="task_model" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{81D89370-CEDE-024B-8FFC-AA5750DB51D0}" name="task_model_better" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{9ED5B514-B946-0E46-8CC4-65EB2916205D}" name="task_name" dataDxfId="152"/>
+    <tableColumn id="2" xr3:uid="{6A16E901-5BDC-D444-B622-2DE255771BB6}" name="task_name_better" dataDxfId="151"/>
+    <tableColumn id="3" xr3:uid="{851E4485-7C38-814F-9C47-82F349076D30}" name="model_name" dataDxfId="150"/>
+    <tableColumn id="4" xr3:uid="{24C3B122-2693-FC4A-B315-868DA09E553F}" name="model_name_better" dataDxfId="149"/>
+    <tableColumn id="5" xr3:uid="{04A3ECDA-65E9-9147-AE27-A3673EA119E3}" name="task_model" dataDxfId="148"/>
+    <tableColumn id="8" xr3:uid="{81D89370-CEDE-024B-8FFC-AA5750DB51D0}" name="task_model_better" dataDxfId="147">
       <calculatedColumnFormula>Table16[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table16[[#This Row],[model_name_better]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F2AFC60A-9961-DD40-953C-64416062443D}" name="balanced_accuracy_mean" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{A1A30C92-11B7-0F4E-9531-A757846C0FD4}" name="macro_f1_mean" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{F2AFC60A-9961-DD40-953C-64416062443D}" name="balanced_accuracy_mean" dataDxfId="146"/>
+    <tableColumn id="7" xr3:uid="{A1A30C92-11B7-0F4E-9531-A757846C0FD4}" name="macro_f1_mean" dataDxfId="145"/>
     <tableColumn id="9" xr3:uid="{4F65909F-B121-AE44-AF11-294868465FDF}" name="Random Baseline"/>
-    <tableColumn id="10" xr3:uid="{9C58D4C4-EF0C-8C46-B6CD-9C7A533B4EE4}" name="RelativeImprovementOverBaseline" dataDxfId="1">
+    <tableColumn id="10" xr3:uid="{9C58D4C4-EF0C-8C46-B6CD-9C7A533B4EE4}" name="RelativeImprovementOverBaseline" dataDxfId="144">
       <calculatedColumnFormula>(Table16[[#This Row],[balanced_accuracy_mean]]-Table16[[#This Row],[Random Baseline]]) / Table16[[#This Row],[Random Baseline]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -19707,100 +20077,100 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="81" t="s">
+      <c r="A61" s="80" t="s">
         <v>203</v>
       </c>
-      <c r="B61" s="82" t="s">
+      <c r="B61" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="C61" s="82" t="s">
+      <c r="C61" s="81" t="s">
         <v>301</v>
       </c>
-      <c r="D61" s="83">
+      <c r="D61" s="82">
         <v>0.69674609473054705</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="81" t="s">
+      <c r="A62" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="82" t="s">
+      <c r="B62" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C62" s="82" t="s">
+      <c r="C62" s="81" t="s">
         <v>237</v>
       </c>
-      <c r="D62" s="83">
+      <c r="D62" s="82">
         <v>0.27008932574240302</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="81" t="s">
+      <c r="A63" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="B63" s="82" t="s">
+      <c r="B63" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C63" s="82" t="s">
+      <c r="C63" s="81" t="s">
         <v>248</v>
       </c>
-      <c r="D63" s="83">
+      <c r="D63" s="82">
         <v>0.65693740471687101</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="81" t="s">
+      <c r="A64" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="B64" s="82" t="s">
+      <c r="B64" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C64" s="82" t="s">
+      <c r="C64" s="81" t="s">
         <v>259</v>
       </c>
-      <c r="D64" s="83">
+      <c r="D64" s="82">
         <v>0.57259215625580095</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="81" t="s">
+      <c r="A65" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="B65" s="82" t="s">
+      <c r="B65" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C65" s="82" t="s">
+      <c r="C65" s="81" t="s">
         <v>270</v>
       </c>
-      <c r="D65" s="83">
+      <c r="D65" s="82">
         <v>0.34764287719168802</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="81" t="s">
+      <c r="A66" s="80" t="s">
         <v>171</v>
       </c>
-      <c r="B66" s="82" t="s">
+      <c r="B66" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C66" s="82" t="s">
+      <c r="C66" s="81" t="s">
         <v>281</v>
       </c>
-      <c r="D66" s="83">
+      <c r="D66" s="82">
         <v>0.45859312840569499</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="81" t="s">
+      <c r="A67" s="80" t="s">
         <v>203</v>
       </c>
-      <c r="B67" s="82" t="s">
+      <c r="B67" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="82" t="s">
+      <c r="C67" s="81" t="s">
         <v>292</v>
       </c>
-      <c r="D67" s="83">
+      <c r="D67" s="82">
         <v>0.65776007324708796</v>
       </c>
     </row>
@@ -20976,7 +21346,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24BEF2CB-CB5C-DF43-B35C-741C03276008}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -21327,6 +21697,22 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19">
+        <f>AVERAGE(F3:F13)</f>
+        <v>0.26067879184124626</v>
+      </c>
+      <c r="G14" s="19">
+        <f>AVERAGE(G3:G13)</f>
+        <v>0.23648106689674356</v>
+      </c>
+      <c r="H14" s="18"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -21337,732 +21723,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E48053-9C4F-6041-863F-8DEBF22B0C3D}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>312</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38" t="str">
-        <f>A1</f>
-        <v>task_name</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C2" s="34" t="s">
-        <v>307</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="E2" s="34" t="str">
-        <f>_xlfn.CONCAT(A2, " - ",C2)</f>
-        <v>task_name - Random</v>
-      </c>
-      <c r="F2" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="F3" s="54">
-        <v>0.65693740471687101</v>
-      </c>
-      <c r="G3" s="54">
-        <v>0.68208073893398302</v>
-      </c>
-      <c r="H3" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>257</v>
-      </c>
-      <c r="F4" s="54">
-        <v>0.65831235479147199</v>
-      </c>
-      <c r="G4" s="53">
-        <v>0.68346967094123001</v>
-      </c>
-      <c r="H4" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="F5" s="54">
-        <v>0.65838804078415203</v>
-      </c>
-      <c r="G5" s="54">
-        <v>0.68349565015250702</v>
-      </c>
-      <c r="H5" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="F6" s="53">
-        <v>0.66043166910492002</v>
-      </c>
-      <c r="G6" s="54">
-        <v>0.68279464082118002</v>
-      </c>
-      <c r="H6" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>316</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>249</v>
-      </c>
-      <c r="F7" s="54">
-        <v>0.668837708052195</v>
-      </c>
-      <c r="G7" s="54">
-        <v>0.69531876727911901</v>
-      </c>
-      <c r="H7" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="F8" s="54">
-        <v>0.67095073120098803</v>
-      </c>
-      <c r="G8" s="54">
-        <v>0.69777479592314495</v>
-      </c>
-      <c r="H8" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>255</v>
-      </c>
-      <c r="F9" s="54">
-        <v>0.71707070080305901</v>
-      </c>
-      <c r="G9" s="54">
-        <v>0.74418657237458496</v>
-      </c>
-      <c r="H9" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="F10" s="54">
-        <v>0.72374581361208501</v>
-      </c>
-      <c r="G10" s="53">
-        <v>0.73700339313221797</v>
-      </c>
-      <c r="H10" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>256</v>
-      </c>
-      <c r="F11" s="53">
-        <v>0.73857218814408898</v>
-      </c>
-      <c r="G11" s="54">
-        <v>0.75266747316967397</v>
-      </c>
-      <c r="H11" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="F12" s="54">
-        <v>0.765450294311946</v>
-      </c>
-      <c r="G12" s="54">
-        <v>0.74922278638737005</v>
-      </c>
-      <c r="H12" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="F13" s="55">
-        <v>0.78742267907035202</v>
-      </c>
-      <c r="G13" s="56">
-        <v>0.79550003135748604</v>
-      </c>
-      <c r="H13" s="39">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EA9A68B-7F28-0B42-81B4-F936174C64E3}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.1640625" customWidth="1"/>
-    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="50" t="s">
-        <v>324</v>
-      </c>
-      <c r="C1" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>312</v>
-      </c>
-      <c r="E1" s="51" t="s">
-        <v>235</v>
-      </c>
-      <c r="F1" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="51" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38" t="str">
-        <f>A1</f>
-        <v>task_name</v>
-      </c>
-      <c r="B2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C2" s="34" t="s">
-        <v>307</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="E2" s="34" t="str">
-        <f>_xlfn.CONCAT(A2, " - ",C2)</f>
-        <v>task_name - Random</v>
-      </c>
-      <c r="F2" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="F3" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="54">
-        <v>0.41270394467837801</v>
-      </c>
-      <c r="H3" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="F4" s="54">
-        <v>0.52132499653409303</v>
-      </c>
-      <c r="G4" s="54">
-        <v>0.51289203208991596</v>
-      </c>
-      <c r="H4" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="F5" s="54">
-        <v>0.54934216999991203</v>
-      </c>
-      <c r="G5" s="54">
-        <v>0.54146896120195198</v>
-      </c>
-      <c r="H5" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" t="s">
-        <v>323</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="F6" s="54">
-        <v>0.554791363897845</v>
-      </c>
-      <c r="G6" s="54">
-        <v>0.55944030191242999</v>
-      </c>
-      <c r="H6" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>316</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>260</v>
-      </c>
-      <c r="F7" s="54">
-        <v>0.55833869403457703</v>
-      </c>
-      <c r="G7" s="54">
-        <v>0.55399818557025704</v>
-      </c>
-      <c r="H7" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" t="s">
-        <v>323</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>263</v>
-      </c>
-      <c r="F8" s="54">
-        <v>0.55836682962401596</v>
-      </c>
-      <c r="G8" s="54">
-        <v>0.56276213382568396</v>
-      </c>
-      <c r="H8" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B9" t="s">
-        <v>323</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="F9" s="53">
-        <v>0.56140121808677201</v>
-      </c>
-      <c r="G9" s="54">
-        <v>0.56025325680567994</v>
-      </c>
-      <c r="H9" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" t="s">
-        <v>323</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>259</v>
-      </c>
-      <c r="F10" s="54">
-        <v>0.57259215625580095</v>
-      </c>
-      <c r="G10" s="53">
-        <v>0.57526024921223495</v>
-      </c>
-      <c r="H10" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>262</v>
-      </c>
-      <c r="F11" s="54">
-        <v>0.57620999965739295</v>
-      </c>
-      <c r="G11" s="54">
-        <v>0.57708392278777598</v>
-      </c>
-      <c r="H11" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" t="s">
-        <v>323</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>265</v>
-      </c>
-      <c r="F12" s="54">
-        <v>0.60023140650857298</v>
-      </c>
-      <c r="G12" s="54">
-        <v>0.55454494330680404</v>
-      </c>
-      <c r="H12" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" t="s">
-        <v>323</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="F13" s="55">
-        <v>0.61577722349836606</v>
-      </c>
-      <c r="G13" s="56">
-        <v>0.58346027103902198</v>
-      </c>
-      <c r="H13" s="39">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88CA99C2-C15D-2549-A483-ABFF94C88A3B}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -22414,6 +22076,18 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D14" s="18"/>
+      <c r="F14" s="13">
+        <f>AVERAGE(F3:F13)</f>
+        <v>0.36117550487910732</v>
+      </c>
+      <c r="G14" s="13">
+        <f>AVERAGE(G3:G13)</f>
+        <v>0.34777038208093181</v>
+      </c>
+      <c r="H14" s="39"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -22423,9 +22097,383 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E48053-9C4F-6041-863F-8DEBF22B0C3D}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="38" t="str">
+        <f>A1</f>
+        <v>task_name</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="E2" s="34" t="str">
+        <f>_xlfn.CONCAT(A2, " - ",C2)</f>
+        <v>task_name - Random</v>
+      </c>
+      <c r="F2" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="F3" s="54">
+        <v>0.65693740471687101</v>
+      </c>
+      <c r="G3" s="54">
+        <v>0.68208073893398302</v>
+      </c>
+      <c r="H3" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="F4" s="54">
+        <v>0.65831235479147199</v>
+      </c>
+      <c r="G4" s="53">
+        <v>0.68346967094123001</v>
+      </c>
+      <c r="H4" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="F5" s="54">
+        <v>0.65838804078415203</v>
+      </c>
+      <c r="G5" s="54">
+        <v>0.68349565015250702</v>
+      </c>
+      <c r="H5" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="F6" s="53">
+        <v>0.66043166910492002</v>
+      </c>
+      <c r="G6" s="54">
+        <v>0.68279464082118002</v>
+      </c>
+      <c r="H6" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="F7" s="54">
+        <v>0.668837708052195</v>
+      </c>
+      <c r="G7" s="54">
+        <v>0.69531876727911901</v>
+      </c>
+      <c r="H7" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="F8" s="54">
+        <v>0.67095073120098803</v>
+      </c>
+      <c r="G8" s="54">
+        <v>0.69777479592314495</v>
+      </c>
+      <c r="H8" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="F9" s="54">
+        <v>0.71707070080305901</v>
+      </c>
+      <c r="G9" s="54">
+        <v>0.74418657237458496</v>
+      </c>
+      <c r="H9" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="F10" s="54">
+        <v>0.72374581361208501</v>
+      </c>
+      <c r="G10" s="53">
+        <v>0.73700339313221797</v>
+      </c>
+      <c r="H10" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="F11" s="53">
+        <v>0.73857218814408898</v>
+      </c>
+      <c r="G11" s="54">
+        <v>0.75266747316967397</v>
+      </c>
+      <c r="H11" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="F12" s="54">
+        <v>0.765450294311946</v>
+      </c>
+      <c r="G12" s="54">
+        <v>0.74922278638737005</v>
+      </c>
+      <c r="H12" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="F13" s="55">
+        <v>0.78742267907035202</v>
+      </c>
+      <c r="G13" s="56">
+        <v>0.79550003135748604</v>
+      </c>
+      <c r="H13" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D14" s="18"/>
+      <c r="F14" s="13">
+        <f>AVERAGE(F3:F13)</f>
+        <v>0.70055632587201178</v>
+      </c>
+      <c r="G14" s="13">
+        <f>AVERAGE(G3:G13)</f>
+        <v>0.71850132004295431</v>
+      </c>
+      <c r="H14" s="39"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E2F406-7CF1-9147-8592-032FB1B0D550}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -22777,6 +22825,392 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D14" s="18"/>
+      <c r="F14" s="13">
+        <f>AVERAGE(F3:F13)</f>
+        <v>0.47729296418519523</v>
+      </c>
+      <c r="G14" s="13">
+        <f>AVERAGE(G3:G13)</f>
+        <v>0.4787120174127662</v>
+      </c>
+      <c r="H14" s="39"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EA9A68B-7F28-0B42-81B4-F936174C64E3}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" customWidth="1"/>
+    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>235</v>
+      </c>
+      <c r="F1" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="51" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="38" t="str">
+        <f>A1</f>
+        <v>task_name</v>
+      </c>
+      <c r="B2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="E2" s="34" t="str">
+        <f>_xlfn.CONCAT(A2, " - ",C2)</f>
+        <v>task_name - Random</v>
+      </c>
+      <c r="F2" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="F3" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="54">
+        <v>0.41270394467837801</v>
+      </c>
+      <c r="H3" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="F4" s="54">
+        <v>0.52132499653409303</v>
+      </c>
+      <c r="G4" s="54">
+        <v>0.51289203208991596</v>
+      </c>
+      <c r="H4" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="F5" s="54">
+        <v>0.54934216999991203</v>
+      </c>
+      <c r="G5" s="54">
+        <v>0.54146896120195198</v>
+      </c>
+      <c r="H5" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="F6" s="54">
+        <v>0.554791363897845</v>
+      </c>
+      <c r="G6" s="54">
+        <v>0.55944030191242999</v>
+      </c>
+      <c r="H6" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s">
+        <v>323</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="F7" s="54">
+        <v>0.55833869403457703</v>
+      </c>
+      <c r="G7" s="54">
+        <v>0.55399818557025704</v>
+      </c>
+      <c r="H7" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="F8" s="54">
+        <v>0.55836682962401596</v>
+      </c>
+      <c r="G8" s="54">
+        <v>0.56276213382568396</v>
+      </c>
+      <c r="H8" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s">
+        <v>323</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9" s="53">
+        <v>0.56140121808677201</v>
+      </c>
+      <c r="G9" s="54">
+        <v>0.56025325680567994</v>
+      </c>
+      <c r="H9" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="F10" s="54">
+        <v>0.57259215625580095</v>
+      </c>
+      <c r="G10" s="53">
+        <v>0.57526024921223495</v>
+      </c>
+      <c r="H10" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="F11" s="54">
+        <v>0.57620999965739295</v>
+      </c>
+      <c r="G11" s="54">
+        <v>0.57708392278777598</v>
+      </c>
+      <c r="H11" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" t="s">
+        <v>323</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="F12" s="54">
+        <v>0.60023140650857298</v>
+      </c>
+      <c r="G12" s="54">
+        <v>0.55454494330680404</v>
+      </c>
+      <c r="H12" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" t="s">
+        <v>323</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="F13" s="55">
+        <v>0.61577722349836606</v>
+      </c>
+      <c r="G13" s="56">
+        <v>0.58346027103902198</v>
+      </c>
+      <c r="H13" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D14" s="18"/>
+      <c r="F14" s="13">
+        <f>AVERAGE(F3:F13)</f>
+        <v>0.56076145982703163</v>
+      </c>
+      <c r="G14" s="13">
+        <f>AVERAGE(G3:G13)</f>
+        <v>0.54489710931183033</v>
+      </c>
+      <c r="H14" s="39"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -22788,7 +23222,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71076070-B6D6-C345-8694-388486D68525}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -23139,6 +23573,18 @@
       <c r="H13" s="39">
         <v>0</v>
       </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D14" s="18"/>
+      <c r="F14" s="13">
+        <f>AVERAGE(F3:F13)</f>
+        <v>0.68980000691247101</v>
+      </c>
+      <c r="G14" s="13">
+        <f>AVERAGE(G3:G13)</f>
+        <v>0.69836068813781849</v>
+      </c>
+      <c r="H14" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23165,7 +23611,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="73" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="51" t="s">
@@ -23183,10 +23629,10 @@
       <c r="F1" s="51" t="s">
         <v>330</v>
       </c>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="75" t="s">
+      <c r="H1" s="74" t="s">
         <v>10</v>
       </c>
       <c r="I1" s="51" t="s">
@@ -23198,212 +23644,212 @@
     </row>
     <row r="2" spans="1:10" ht="35" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A2" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="58" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>314</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>278</v>
+      </c>
+      <c r="F2" s="75" t="str">
+        <f>Table16[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table16[[#This Row],[model_name_better]]</f>
+        <v>Four Provinces
+SVM (Linear)</v>
+      </c>
+      <c r="G2" s="83">
+        <v>0.39387690904640299</v>
+      </c>
+      <c r="H2" s="60">
+        <v>0.38084229333062602</v>
+      </c>
+      <c r="I2" s="79">
+        <v>0.25</v>
+      </c>
+      <c r="J2" s="13">
+        <f>(Table16[[#This Row],[balanced_accuracy_mean]]-Table16[[#This Row],[Random Baseline]]) / Table16[[#This Row],[Random Baseline]]</f>
+        <v>0.57550763618561196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>332</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>309</v>
+      </c>
+      <c r="E3" s="57" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" s="76" t="str">
+        <f>Table16[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table16[[#This Row],[model_name_better]]</f>
+        <v>Dáil vs Northern Ireland
+Naive Bayes</v>
+      </c>
+      <c r="G3" s="63">
+        <v>0.78742267907035202</v>
+      </c>
+      <c r="H3" s="64">
+        <v>0.79550003135748604</v>
+      </c>
+      <c r="I3" s="79">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="13">
+        <f>(Table16[[#This Row],[balanced_accuracy_mean]]-Table16[[#This Row],[Random Baseline]]) / Table16[[#This Row],[Random Baseline]]</f>
+        <v>0.57484535814070403</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A4" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="66" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4" s="67" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>310</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>290</v>
+      </c>
+      <c r="F4" s="77" t="str">
+        <f>Table16[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table16[[#This Row],[model_name_better]]</f>
+        <v>Ulster, Leinster, and Rest
+SVM (RBF Kernel)</v>
+      </c>
+      <c r="G4" s="69">
+        <v>0.52408969936051997</v>
+      </c>
+      <c r="H4" s="78">
+        <v>0.51867425524064803</v>
+      </c>
+      <c r="I4" s="79">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="J4" s="13">
+        <f>(Table16[[#This Row],[balanced_accuracy_mean]]-Table16[[#This Row],[Random Baseline]]) / Table16[[#This Row],[Random Baseline]]</f>
+        <v>0.57242634071563159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A5" s="57" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>336</v>
+      </c>
+      <c r="C5" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="E5" s="57" t="s">
+        <v>297</v>
+      </c>
+      <c r="F5" s="76" t="str">
+        <f>Table16[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table16[[#This Row],[model_name_better]]</f>
+        <v>Ulster vs Rest
+Logistic Regression (Weighted)</v>
+      </c>
+      <c r="G5" s="72">
+        <v>0.74775796701111596</v>
+      </c>
+      <c r="H5" s="64">
+        <v>0.74442445336057095</v>
+      </c>
+      <c r="I5" s="79">
+        <v>0.5</v>
+      </c>
+      <c r="J5" s="13">
+        <f>(Table16[[#This Row],[balanced_accuracy_mean]]-Table16[[#This Row],[Random Baseline]]) / Table16[[#This Row],[Random Baseline]]</f>
+        <v>0.49551593402223193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A6" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="71" t="s">
+        <v>333</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>264</v>
+      </c>
+      <c r="F6" s="76" t="str">
+        <f>Table16[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table16[[#This Row],[model_name_better]]</f>
+        <v>Leinster vs Rest
+Logistic Regression (Weighted)</v>
+      </c>
+      <c r="G6" s="72">
+        <v>0.61580000000000001</v>
+      </c>
+      <c r="H6" s="70">
+        <v>0.58350000000000002</v>
+      </c>
+      <c r="I6" s="79">
+        <v>0.5</v>
+      </c>
+      <c r="J6" s="13">
+        <f>(Table16[[#This Row],[balanced_accuracy_mean]]-Table16[[#This Row],[Random Baseline]]) / Table16[[#This Row],[Random Baseline]]</f>
+        <v>0.23160000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A7" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B7" s="61" t="s">
         <v>331</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C7" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D7" s="59" t="s">
         <v>321</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E7" s="57" t="s">
         <v>241</v>
       </c>
-      <c r="F2" s="76" t="str">
+      <c r="F7" s="76" t="str">
         <f>Table16[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table16[[#This Row],[model_name_better]]</f>
         <v>Dáil Speakers
 Logistic Regression</v>
       </c>
-      <c r="G2" s="60">
+      <c r="G7" s="72">
         <v>0.27210886725816702</v>
       </c>
-      <c r="H2" s="61">
+      <c r="H7" s="70">
         <v>0.25396344765783402</v>
       </c>
-      <c r="I2" s="80">
+      <c r="I7" s="79">
         <v>0.25</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J7" s="13">
         <f>(Table16[[#This Row],[balanced_accuracy_mean]]-Table16[[#This Row],[Random Baseline]]) / Table16[[#This Row],[Random Baseline]]</f>
         <v>8.8435469032668079E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A3" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" s="62" t="s">
-        <v>334</v>
-      </c>
-      <c r="C3" s="63" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="59" t="s">
-        <v>314</v>
-      </c>
-      <c r="E3" s="57" t="s">
-        <v>278</v>
-      </c>
-      <c r="F3" s="77" t="str">
-        <f>Table16[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table16[[#This Row],[model_name_better]]</f>
-        <v>Four Provinces
-SVM (Linear)</v>
-      </c>
-      <c r="G3" s="64">
-        <v>0.39387690904640299</v>
-      </c>
-      <c r="H3" s="71">
-        <v>0.38084229333062602</v>
-      </c>
-      <c r="I3" s="80">
-        <v>0.25</v>
-      </c>
-      <c r="J3" s="13">
-        <f>(Table16[[#This Row],[balanced_accuracy_mean]]-Table16[[#This Row],[Random Baseline]]) / Table16[[#This Row],[Random Baseline]]</f>
-        <v>0.57550763618561196</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="66" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="67" t="s">
-        <v>335</v>
-      </c>
-      <c r="C4" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="69" t="s">
-        <v>310</v>
-      </c>
-      <c r="E4" s="66" t="s">
-        <v>290</v>
-      </c>
-      <c r="F4" s="78" t="str">
-        <f>Table16[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table16[[#This Row],[model_name_better]]</f>
-        <v>Ulster, Leinster, and Rest
-SVM (RBF Kernel)</v>
-      </c>
-      <c r="G4" s="70">
-        <v>0.52408969936051997</v>
-      </c>
-      <c r="H4" s="79">
-        <v>0.51867425524064803</v>
-      </c>
-      <c r="I4" s="80">
-        <v>0.33329999999999999</v>
-      </c>
-      <c r="J4" s="13">
-        <f>(Table16[[#This Row],[balanced_accuracy_mean]]-Table16[[#This Row],[Random Baseline]]) / Table16[[#This Row],[Random Baseline]]</f>
-        <v>0.57242634071563159</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A5" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="62" t="s">
-        <v>333</v>
-      </c>
-      <c r="C5" s="63" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="59" t="s">
-        <v>320</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>264</v>
-      </c>
-      <c r="F5" s="77" t="str">
-        <f>Table16[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table16[[#This Row],[model_name_better]]</f>
-        <v>Leinster vs Rest
-Logistic Regression (Weighted)</v>
-      </c>
-      <c r="G5" s="73">
-        <v>0.61580000000000001</v>
-      </c>
-      <c r="H5" s="71">
-        <v>0.58350000000000002</v>
-      </c>
-      <c r="I5" s="80">
-        <v>0.5</v>
-      </c>
-      <c r="J5" s="13">
-        <f>(Table16[[#This Row],[balanced_accuracy_mean]]-Table16[[#This Row],[Random Baseline]]) / Table16[[#This Row],[Random Baseline]]</f>
-        <v>0.23160000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A6" s="57" t="s">
-        <v>203</v>
-      </c>
-      <c r="B6" s="72" t="s">
-        <v>336</v>
-      </c>
-      <c r="C6" s="63" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>320</v>
-      </c>
-      <c r="E6" s="57" t="s">
-        <v>297</v>
-      </c>
-      <c r="F6" s="77" t="str">
-        <f>Table16[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table16[[#This Row],[model_name_better]]</f>
-        <v>Ulster vs Rest
-Logistic Regression (Weighted)</v>
-      </c>
-      <c r="G6" s="73">
-        <v>0.74775796701111596</v>
-      </c>
-      <c r="H6" s="65">
-        <v>0.74442445336057095</v>
-      </c>
-      <c r="I6" s="80">
-        <v>0.5</v>
-      </c>
-      <c r="J6" s="13">
-        <f>(Table16[[#This Row],[balanced_accuracy_mean]]-Table16[[#This Row],[Random Baseline]]) / Table16[[#This Row],[Random Baseline]]</f>
-        <v>0.49551593402223193</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A7" s="57" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="62" t="s">
-        <v>332</v>
-      </c>
-      <c r="C7" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="59" t="s">
-        <v>309</v>
-      </c>
-      <c r="E7" s="57" t="s">
-        <v>254</v>
-      </c>
-      <c r="F7" s="77" t="str">
-        <f>Table16[[#This Row],[task_name_better]] &amp; CHAR(10) &amp; Table16[[#This Row],[model_name_better]]</f>
-        <v>Dáil vs Northern Ireland
-Naive Bayes</v>
-      </c>
-      <c r="G7" s="64">
-        <v>0.78742267907035202</v>
-      </c>
-      <c r="H7" s="65">
-        <v>0.79550003135748604</v>
-      </c>
-      <c r="I7" s="80">
-        <v>0.5</v>
-      </c>
-      <c r="J7" s="13">
-        <f>(Table16[[#This Row],[balanced_accuracy_mean]]-Table16[[#This Row],[Random Baseline]]) / Table16[[#This Row],[Random Baseline]]</f>
-        <v>0.57484535814070403</v>
       </c>
     </row>
   </sheetData>
